--- a/data/trans_orig/Q4506_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q4506_R-Provincia-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 50 o mayor el pasado verano al aire libre en 2012</t>
+          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 50 o mayor el pasado verano al aire libre en 2012 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>11617</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30664</t>
+          <t>30384</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>64134</t>
+          <t>65214</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>97048</t>
+          <t>96400</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78992</t>
+          <t>80976</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>117452</t>
+          <t>119508</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8613</t>
+          <t>8334</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24421</t>
+          <t>24794</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19376</t>
+          <t>19262</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41042</t>
+          <t>41260</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31754</t>
+          <t>30883</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58294</t>
+          <t>58577</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9292</t>
+          <t>9472</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26775</t>
+          <t>27179</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18189</t>
+          <t>17720</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>39001</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>31207</t>
+          <t>31337</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>57632</t>
+          <t>57630</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9208</t>
+          <t>9100</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26150</t>
+          <t>25928</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14553</t>
+          <t>13535</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14162</t>
+          <t>14744</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34093</t>
+          <t>34498</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>210576</t>
+          <t>210778</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>242625</t>
+          <t>242270</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>125696</t>
+          <t>123409</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>159822</t>
+          <t>159858</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>348019</t>
+          <t>348149</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>397203</t>
+          <t>396104</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,29%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37023</t>
+          <t>36577</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65885</t>
+          <t>64470</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>77249</t>
+          <t>75898</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>112839</t>
+          <t>112487</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121720</t>
+          <t>121025</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>169514</t>
+          <t>166605</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19128</t>
+          <t>18707</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43282</t>
+          <t>42504</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33222</t>
+          <t>33080</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>58306</t>
+          <t>58180</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>57381</t>
+          <t>57979</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>92308</t>
+          <t>92357</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51454</t>
+          <t>53048</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>83730</t>
+          <t>85777</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>76610</t>
+          <t>76662</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>112533</t>
+          <t>114103</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>139256</t>
+          <t>137866</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>188981</t>
+          <t>189150</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31196</t>
+          <t>30916</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57934</t>
+          <t>57798</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32913</t>
+          <t>31699</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61625</t>
+          <t>60668</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>72400</t>
+          <t>69838</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>108495</t>
+          <t>109085</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>290380</t>
+          <t>290136</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>338286</t>
+          <t>337210</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>222122</t>
+          <t>222203</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>269347</t>
+          <t>266407</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>527037</t>
+          <t>528054</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>594081</t>
+          <t>593160</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,69%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24671</t>
+          <t>25463</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48756</t>
+          <t>48377</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>87690</t>
+          <t>90428</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>123094</t>
+          <t>125155</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>119581</t>
+          <t>121697</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>166828</t>
+          <t>163865</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28895</t>
+          <t>29121</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>54469</t>
+          <t>55136</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46813</t>
+          <t>47275</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75519</t>
+          <t>76805</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81923</t>
+          <t>81279</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>122290</t>
+          <t>118791</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>55949</t>
+          <t>55052</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>84707</t>
+          <t>85427</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38910</t>
+          <t>41809</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>67316</t>
+          <t>69572</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>102195</t>
+          <t>102586</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>141736</t>
+          <t>143780</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,68%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42027</t>
+          <t>41947</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>68780</t>
+          <t>70919</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16996</t>
+          <t>17449</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37717</t>
+          <t>37149</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>64593</t>
+          <t>64538</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>99689</t>
+          <t>99784</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>106298</t>
+          <t>105489</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>141022</t>
+          <t>138241</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,82 +2562,82 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>32,74%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>42,91%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>96223</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>79795</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>113058</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>28,22%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>23,4%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>33,15%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>218822</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>195971</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>246188</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
           <t>32,99%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>43,77%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>96223</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>80335</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>114705</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>28,22%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>23,56%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>33,64%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>218822</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>195640</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>246560</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>32,99%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,12%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12492</t>
+          <t>12584</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31712</t>
+          <t>31321</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>66934</t>
+          <t>66620</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>98598</t>
+          <t>98925</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>85550</t>
+          <t>85266</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>123784</t>
+          <t>123216</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7238</t>
+          <t>8179</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22386</t>
+          <t>22901</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>20444</t>
+          <t>19996</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>43101</t>
+          <t>41134</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>32442</t>
+          <t>31892</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>57987</t>
+          <t>58331</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8667</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24232</t>
+          <t>25582</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>44312</t>
+          <t>44651</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>73121</t>
+          <t>72834</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>58177</t>
+          <t>57884</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>90640</t>
+          <t>92173</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19904</t>
+          <t>19159</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41160</t>
+          <t>40716</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15677</t>
+          <t>16757</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36180</t>
+          <t>36563</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>41448</t>
+          <t>40539</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>71758</t>
+          <t>70716</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>277229</t>
+          <t>275743</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>309849</t>
+          <t>309307</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>175296</t>
+          <t>176856</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>215614</t>
+          <t>215754</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>459613</t>
+          <t>460479</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>514908</t>
+          <t>514092</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,47%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>3255</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>16554</t>
+          <t>16183</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>24820</t>
+          <t>25141</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>48610</t>
+          <t>47655</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>32167</t>
+          <t>32746</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>57299</t>
+          <t>57783</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13670</t>
+          <t>13743</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>31832</t>
+          <t>31112</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>24115</t>
+          <t>24508</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>46832</t>
+          <t>46346</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>42447</t>
+          <t>43989</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>71618</t>
+          <t>71554</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20821</t>
+          <t>20407</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>41381</t>
+          <t>42029</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>39006</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>64008</t>
+          <t>63676</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>64314</t>
+          <t>63718</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>97318</t>
+          <t>96981</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>24259</t>
+          <t>23315</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>45426</t>
+          <t>45158</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>19088</t>
+          <t>18373</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>39300</t>
+          <t>38771</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>48272</t>
+          <t>48135</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>76862</t>
+          <t>76868</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>104195</t>
+          <t>102181</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>132906</t>
+          <t>133582</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>58315</t>
+          <t>57993</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>86893</t>
+          <t>88253</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>170650</t>
+          <t>172826</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>213127</t>
+          <t>213908</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,49%</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>27565</t>
+          <t>28698</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>51272</t>
+          <t>52335</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>58482</t>
+          <t>58412</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>87405</t>
+          <t>88405</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>95495</t>
+          <t>93116</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>133491</t>
+          <t>132565</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>21530</t>
+          <t>20514</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>42846</t>
+          <t>42263</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>25486</t>
+          <t>25653</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>47729</t>
+          <t>48561</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>52950</t>
+          <t>52421</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>84209</t>
+          <t>83477</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,07%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>35725</t>
+          <t>37464</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>62879</t>
+          <t>63814</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>44465</t>
+          <t>43727</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>71657</t>
+          <t>70466</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>86713</t>
+          <t>87948</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>126103</t>
+          <t>126285</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,79%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>44011</t>
+          <t>45959</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>72872</t>
+          <t>73548</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>25856</t>
+          <t>26101</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>48765</t>
+          <t>48040</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>78030</t>
+          <t>77440</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>113869</t>
+          <t>112807</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>81604</t>
+          <t>81987</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>113472</t>
+          <t>113782</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>63603</t>
+          <t>63980</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>94278</t>
+          <t>95081</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>154335</t>
+          <t>151195</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>197222</t>
+          <t>196527</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,47%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>43877</t>
+          <t>45322</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>74583</t>
+          <t>75445</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>128104</t>
+          <t>131270</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>175187</t>
+          <t>177568</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>181588</t>
+          <t>184100</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>237706</t>
+          <t>239341</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,67%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>47568</t>
+          <t>48842</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>81597</t>
+          <t>82492</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>76064</t>
+          <t>77451</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>114510</t>
+          <t>114332</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>134706</t>
+          <t>137064</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>184456</t>
+          <t>185400</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>100823</t>
+          <t>103186</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>143767</t>
+          <t>148025</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>125299</t>
+          <t>124341</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>168715</t>
+          <t>166670</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>241824</t>
+          <t>238952</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>298438</t>
+          <t>296701</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,9%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>118369</t>
+          <t>116419</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>161647</t>
+          <t>159257</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>58049</t>
+          <t>59944</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>90817</t>
+          <t>93423</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>184621</t>
+          <t>187349</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>239211</t>
+          <t>240654</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,76%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>252114</t>
+          <t>253641</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>306286</t>
+          <t>306282</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>202461</t>
+          <t>201236</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>252549</t>
+          <t>253257</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>472627</t>
+          <t>471150</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>545268</t>
+          <t>547769</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,43%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>24923</t>
+          <t>25969</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>50627</t>
+          <t>51044</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>71636</t>
+          <t>70812</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>107681</t>
+          <t>111025</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>104118</t>
+          <t>100004</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>149594</t>
+          <t>147482</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>86033</t>
+          <t>85089</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>125097</t>
+          <t>123630</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>166812</t>
+          <t>168398</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>218397</t>
+          <t>217028</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>266818</t>
+          <t>268474</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>328339</t>
+          <t>333922</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>126831</t>
+          <t>121817</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>170979</t>
+          <t>169652</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>146737</t>
+          <t>148074</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>195212</t>
+          <t>195257</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>285621</t>
+          <t>285045</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>351609</t>
+          <t>356571</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>51944</t>
+          <t>53956</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>84560</t>
+          <t>85308</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>51169</t>
+          <t>51771</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>84147</t>
+          <t>84798</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>112447</t>
+          <t>111320</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>157871</t>
+          <t>157320</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>391876</t>
+          <t>393075</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>450537</t>
+          <t>449210</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>271734</t>
+          <t>273293</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>332197</t>
+          <t>328995</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>683957</t>
+          <t>681665</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>764515</t>
+          <t>764012</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>47,88%</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>237938</t>
+          <t>238341</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>301895</t>
+          <t>299975</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6202,12 +6202,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>664050</t>
+          <t>661393</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>763842</t>
+          <t>760420</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>911490</t>
+          <t>916521</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>1036080</t>
+          <t>1034154</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -6300,12 +6300,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>284114</t>
+          <t>284021</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>355489</t>
+          <t>351772</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>473793</t>
+          <t>478189</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>562163</t>
+          <t>562433</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>781497</t>
+          <t>785808</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>896064</t>
+          <t>900498</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>478571</t>
+          <t>470397</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>560521</t>
+          <t>561053</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>606279</t>
+          <t>612613</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>706445</t>
+          <t>704010</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>1109561</t>
+          <t>1108717</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>1232492</t>
+          <t>1243764</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6526,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>399099</t>
+          <t>402097</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>479721</t>
+          <t>481800</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>274124</t>
+          <t>272407</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>345549</t>
+          <t>343370</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6596,12 +6596,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>697688</t>
+          <t>695039</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>797203</t>
+          <t>805493</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -6639,12 +6639,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1814187</t>
+          <t>1822258</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>1936800</t>
+          <t>1937460</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>1301182</t>
+          <t>1297622</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1419311</t>
+          <t>1415904</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>3151595</t>
+          <t>3159503</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>3320533</t>
+          <t>3326108</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,72%</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 50 o mayor el pasado verano al aire libre en 2016</t>
+          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 50 o mayor el pasado verano al aire libre en 2016 (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7105,12 +7105,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45123</t>
+          <t>45341</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74966</t>
+          <t>73660</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>135982</t>
+          <t>138362</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>171763</t>
+          <t>171905</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>190527</t>
+          <t>191874</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>238390</t>
+          <t>237958</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,85%</t>
         </is>
       </c>
     </row>
@@ -7218,12 +7218,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10149</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28299</t>
+          <t>26350</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25396</t>
+          <t>25357</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49527</t>
+          <t>46488</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39435</t>
+          <t>40779</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67086</t>
+          <t>69013</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -7331,12 +7331,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19513</t>
+          <t>18230</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40319</t>
+          <t>39987</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>15316</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33624</t>
+          <t>34039</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38134</t>
+          <t>38923</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>67078</t>
+          <t>65531</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -7444,12 +7444,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14259</t>
+          <t>13187</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32829</t>
+          <t>31970</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5500</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20226</t>
+          <t>21837</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22850</t>
+          <t>22759</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48094</t>
+          <t>46807</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7529,12 +7529,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>151156</t>
+          <t>151453</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>185880</t>
+          <t>186680</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>49977</t>
+          <t>49164</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>78316</t>
+          <t>78873</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>206690</t>
+          <t>205827</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>256667</t>
+          <t>255339</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>43,84%</t>
         </is>
       </c>
     </row>
@@ -7787,12 +7787,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45536</t>
+          <t>45208</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75930</t>
+          <t>74641</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>111995</t>
+          <t>112921</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>153518</t>
+          <t>154398</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>166303</t>
+          <t>168265</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>219071</t>
+          <t>219719</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>183982</t>
+          <t>184450</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>227151</t>
+          <t>229524</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>215084</t>
+          <t>215849</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>262564</t>
+          <t>262150</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>412400</t>
+          <t>412535</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>474048</t>
+          <t>475088</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,42%</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>83978</t>
+          <t>83411</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>122495</t>
+          <t>121769</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62488</t>
+          <t>61412</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>96684</t>
+          <t>95245</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>154912</t>
+          <t>155325</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>205565</t>
+          <t>203694</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -8126,12 +8126,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13317</t>
+          <t>13470</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31428</t>
+          <t>31138</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6447</t>
+          <t>6876</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21308</t>
+          <t>21231</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23365</t>
+          <t>22887</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47677</t>
+          <t>45862</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -8239,12 +8239,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>95236</t>
+          <t>95692</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>134678</t>
+          <t>133568</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47555</t>
+          <t>47970</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77289</t>
+          <t>79182</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>150035</t>
+          <t>150811</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>200663</t>
+          <t>200878</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12362</t>
+          <t>11739</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27889</t>
+          <t>27859</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36468</t>
+          <t>35561</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63820</t>
+          <t>62775</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53397</t>
+          <t>53285</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>82975</t>
+          <t>84431</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,93%</t>
         </is>
       </c>
     </row>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13609</t>
+          <t>13815</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32004</t>
+          <t>31580</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17982</t>
+          <t>17147</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37730</t>
+          <t>36410</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36110</t>
+          <t>35442</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60233</t>
+          <t>61201</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22280</t>
+          <t>22569</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>42185</t>
+          <t>42649</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>95136</t>
+          <t>94767</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>128945</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>123132</t>
+          <t>123003</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>164871</t>
+          <t>164269</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -8808,12 +8808,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>64883</t>
+          <t>66273</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>95832</t>
+          <t>96632</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55455</t>
+          <t>55795</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>84956</t>
+          <t>84553</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>126584</t>
+          <t>128097</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>167503</t>
+          <t>169341</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -8921,12 +8921,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>148263</t>
+          <t>148030</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>181516</t>
+          <t>180897</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8956,12 +8956,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>65754</t>
+          <t>67336</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>97338</t>
+          <t>98612</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8991,12 +8991,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>225518</t>
+          <t>224402</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>270329</t>
+          <t>272157</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,68%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52232</t>
+          <t>52237</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>81133</t>
+          <t>82445</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>104420</t>
+          <t>105450</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>141579</t>
+          <t>141829</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>167328</t>
+          <t>166038</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>216430</t>
+          <t>214270</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,33%</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29088</t>
+          <t>27482</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>52927</t>
+          <t>52618</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>34600</t>
+          <t>33610</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>62054</t>
+          <t>60338</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>68262</t>
+          <t>67276</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>103921</t>
+          <t>103421</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9377,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22411</t>
+          <t>22536</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>44946</t>
+          <t>44948</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9392,7 +9392,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>28552</t>
+          <t>28748</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>51728</t>
+          <t>53168</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>56423</t>
+          <t>56683</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>89205</t>
+          <t>87440</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -9490,12 +9490,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18796</t>
+          <t>18094</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>40310</t>
+          <t>40340</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12955</t>
+          <t>13127</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32111</t>
+          <t>31996</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>36644</t>
+          <t>37351</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>64407</t>
+          <t>64707</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -9603,12 +9603,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>184114</t>
+          <t>183888</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>223656</t>
+          <t>223844</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>138083</t>
+          <t>137971</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>176601</t>
+          <t>177942</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>330199</t>
+          <t>333791</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>388274</t>
+          <t>390906</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,69%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>1847</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10471</t>
+          <t>11080</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8373</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>23233</t>
+          <t>23272</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11769</t>
+          <t>12039</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>29123</t>
+          <t>28196</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -9946,12 +9946,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>25858</t>
+          <t>26412</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>47988</t>
+          <t>47818</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9981,12 +9981,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>42952</t>
+          <t>42545</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>67615</t>
+          <t>67027</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>73073</t>
+          <t>75720</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>107364</t>
+          <t>107211</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,94%</t>
         </is>
       </c>
     </row>
@@ -10059,12 +10059,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20162</t>
+          <t>18885</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>37573</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>32467</t>
+          <t>31729</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>55261</t>
+          <t>56237</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>57155</t>
+          <t>57278</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>86819</t>
+          <t>85403</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -10172,12 +10172,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>23417</t>
+          <t>22200</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>44515</t>
+          <t>45507</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>21746</t>
+          <t>21274</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>41096</t>
+          <t>41453</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>50242</t>
+          <t>50042</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>77676</t>
+          <t>78878</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -10285,12 +10285,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>97212</t>
+          <t>96139</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>125915</t>
+          <t>125228</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10300,12 +10300,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>63113</t>
+          <t>63166</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>91332</t>
+          <t>91325</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10335,7 +10335,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>165246</t>
+          <t>166624</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>208955</t>
+          <t>206523</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,05%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>23436</t>
+          <t>23423</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>47201</t>
+          <t>46333</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>32950</t>
+          <t>32252</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>57248</t>
+          <t>55291</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>61721</t>
+          <t>62543</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>94251</t>
+          <t>94489</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,88%</t>
         </is>
       </c>
     </row>
@@ -10628,12 +10628,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>34062</t>
+          <t>34567</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>56828</t>
+          <t>58318</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10643,12 +10643,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10663,12 +10663,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>43059</t>
+          <t>44909</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>69408</t>
+          <t>72360</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>83999</t>
+          <t>84047</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>119418</t>
+          <t>121255</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,95%</t>
         </is>
       </c>
     </row>
@@ -10741,12 +10741,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>19038</t>
+          <t>18309</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>38419</t>
+          <t>38439</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10756,12 +10756,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10776,12 +10776,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>25677</t>
+          <t>24379</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>47975</t>
+          <t>46382</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10811,12 +10811,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>47348</t>
+          <t>48676</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>76613</t>
+          <t>77568</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10826,12 +10826,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -10854,12 +10854,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>5136</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>19298</t>
+          <t>19133</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>2831</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>13338</t>
+          <t>12881</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10904,12 +10904,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>10064</t>
+          <t>9498</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>27311</t>
+          <t>26851</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10939,12 +10939,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -10967,12 +10967,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>128507</t>
+          <t>127716</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>160272</t>
+          <t>160600</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10982,12 +10982,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>110158</t>
+          <t>110270</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>143475</t>
+          <t>142594</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11017,12 +11017,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>246674</t>
+          <t>247429</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>294527</t>
+          <t>292940</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11052,12 +11052,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,44%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>36366</t>
+          <t>36404</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>65430</t>
+          <t>64208</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>103236</t>
+          <t>104224</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>145694</t>
+          <t>146336</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>149042</t>
+          <t>148420</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>198955</t>
+          <t>198199</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -11310,12 +11310,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>65944</t>
+          <t>68105</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>104306</t>
+          <t>102983</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11325,12 +11325,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11345,12 +11345,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>98617</t>
+          <t>99526</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>139211</t>
+          <t>139917</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11360,12 +11360,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>176618</t>
+          <t>176790</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>233425</t>
+          <t>231325</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,34%</t>
         </is>
       </c>
     </row>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>82755</t>
+          <t>82611</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>124742</t>
+          <t>123715</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>105783</t>
+          <t>107890</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>147022</t>
+          <t>149161</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>200396</t>
+          <t>201216</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>260124</t>
+          <t>258651</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11508,12 +11508,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -11536,12 +11536,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>91396</t>
+          <t>93277</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>136166</t>
+          <t>133699</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>63495</t>
+          <t>63132</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>97693</t>
+          <t>97291</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>166806</t>
+          <t>166570</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>218825</t>
+          <t>219058</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11621,12 +11621,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -11649,12 +11649,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>274847</t>
+          <t>274282</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>326066</t>
+          <t>327290</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>211439</t>
+          <t>212085</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>261730</t>
+          <t>263089</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11699,12 +11699,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>501531</t>
+          <t>506137</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>576827</t>
+          <t>582663</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11734,12 +11734,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -11879,12 +11879,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>30863</t>
+          <t>32462</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>58776</t>
+          <t>60325</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>81033</t>
+          <t>78720</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>119710</t>
+          <t>119002</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11949,12 +11949,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>122226</t>
+          <t>119272</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>169730</t>
+          <t>165849</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11964,12 +11964,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>176128</t>
+          <t>173392</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>225427</t>
+          <t>223248</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12007,12 +12007,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12027,12 +12027,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>314143</t>
+          <t>313936</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>370336</t>
+          <t>376543</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12042,12 +12042,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12062,12 +12062,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>501879</t>
+          <t>501918</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>582224</t>
+          <t>580863</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,29%</t>
         </is>
       </c>
     </row>
@@ -12105,12 +12105,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>163342</t>
+          <t>163141</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>209205</t>
+          <t>210221</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12120,12 +12120,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12140,12 +12140,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>148308</t>
+          <t>148165</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>195680</t>
+          <t>195795</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12155,12 +12155,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>319201</t>
+          <t>321278</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>387707</t>
+          <t>390707</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12190,12 +12190,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -12218,12 +12218,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>75785</t>
+          <t>77961</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>112456</t>
+          <t>111357</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>40712</t>
+          <t>41403</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>68810</t>
+          <t>71085</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12268,12 +12268,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>125603</t>
+          <t>126097</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>172822</t>
+          <t>172994</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12303,12 +12303,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -12331,12 +12331,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>225017</t>
+          <t>225741</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>278763</t>
+          <t>279476</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>135700</t>
+          <t>136251</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>182541</t>
+          <t>185770</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12381,12 +12381,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>373926</t>
+          <t>375751</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>448531</t>
+          <t>447662</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12416,12 +12416,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,97%</t>
         </is>
       </c>
     </row>
@@ -12561,12 +12561,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>297102</t>
+          <t>301654</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>370333</t>
+          <t>371322</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12576,12 +12576,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12596,12 +12596,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>682798</t>
+          <t>689529</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>791879</t>
+          <t>784511</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12611,12 +12611,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12631,12 +12631,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>1006133</t>
+          <t>1005046</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>1133260</t>
+          <t>1134760</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12646,12 +12646,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -12674,12 +12674,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>601741</t>
+          <t>602023</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>695710</t>
+          <t>692471</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>869804</t>
+          <t>868070</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>974100</t>
+          <t>977602</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12724,12 +12724,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1493335</t>
+          <t>1500954</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>1637378</t>
+          <t>1639322</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -12787,12 +12787,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>491122</t>
+          <t>492040</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>579815</t>
+          <t>579463</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>577867</t>
+          <t>578316</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>668512</t>
+          <t>668315</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12837,12 +12837,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>1099234</t>
+          <t>1101547</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>1221363</t>
+          <t>1222539</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12872,12 +12872,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -12900,12 +12900,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>360855</t>
+          <t>364918</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>436974</t>
+          <t>441971</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>252221</t>
+          <t>254995</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>317800</t>
+          <t>323173</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12950,12 +12950,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>635888</t>
+          <t>637369</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>739363</t>
+          <t>737097</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12985,12 +12985,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -13013,12 +13013,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1397019</t>
+          <t>1399609</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>1519989</t>
+          <t>1511904</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13028,12 +13028,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13048,12 +13048,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>908037</t>
+          <t>908927</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1016855</t>
+          <t>1016924</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13063,7 +13063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -13083,12 +13083,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>2343967</t>
+          <t>2344262</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>2506472</t>
+          <t>2502378</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13103,7 +13103,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q4506_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q4506_R-Provincia-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11617</t>
+          <t>11864</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30384</t>
+          <t>30750</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>65214</t>
+          <t>65334</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>96400</t>
+          <t>98098</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80976</t>
+          <t>82593</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>119508</t>
+          <t>121440</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,94%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8334</t>
+          <t>8526</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24794</t>
+          <t>24940</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19262</t>
+          <t>18536</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41260</t>
+          <t>39915</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30883</t>
+          <t>32444</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58577</t>
+          <t>58689</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9472</t>
+          <t>9105</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27179</t>
+          <t>24772</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17720</t>
+          <t>18430</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39001</t>
+          <t>39355</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>31337</t>
+          <t>31335</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>57630</t>
+          <t>57898</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9100</t>
+          <t>8694</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25928</t>
+          <t>25587</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3050</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13535</t>
+          <t>14495</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14744</t>
+          <t>14579</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34498</t>
+          <t>34531</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>210778</t>
+          <t>213038</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>242270</t>
+          <t>242755</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>123409</t>
+          <t>125615</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>159858</t>
+          <t>163724</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>348149</t>
+          <t>344976</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>396104</t>
+          <t>394747</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,06%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36577</t>
+          <t>35427</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64470</t>
+          <t>66162</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75898</t>
+          <t>76239</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>112487</t>
+          <t>112335</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121025</t>
+          <t>122542</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>166605</t>
+          <t>169369</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18707</t>
+          <t>18631</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42504</t>
+          <t>42183</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33080</t>
+          <t>32556</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>58180</t>
+          <t>58267</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>57979</t>
+          <t>56813</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>92357</t>
+          <t>92305</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>53048</t>
+          <t>53270</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>85777</t>
+          <t>85512</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>76662</t>
+          <t>77489</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>114103</t>
+          <t>113172</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>137866</t>
+          <t>137910</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>189150</t>
+          <t>187629</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30916</t>
+          <t>32868</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57798</t>
+          <t>59576</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31699</t>
+          <t>33741</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60668</t>
+          <t>61039</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>69838</t>
+          <t>70751</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>109085</t>
+          <t>108485</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>290136</t>
+          <t>289150</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>337210</t>
+          <t>336020</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>222203</t>
+          <t>223307</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>266407</t>
+          <t>269118</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>528054</t>
+          <t>528274</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>593160</t>
+          <t>594471</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,81%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25463</t>
+          <t>24707</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48377</t>
+          <t>49210</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>90428</t>
+          <t>88899</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>125155</t>
+          <t>124865</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>121697</t>
+          <t>122419</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>163865</t>
+          <t>166182</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>25,06%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29121</t>
+          <t>29063</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55136</t>
+          <t>54391</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47275</t>
+          <t>46422</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>76805</t>
+          <t>75927</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81279</t>
+          <t>83469</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>118791</t>
+          <t>120311</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>55052</t>
+          <t>56153</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>85427</t>
+          <t>83712</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41809</t>
+          <t>40282</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>69572</t>
+          <t>67363</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>102586</t>
+          <t>102324</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>143780</t>
+          <t>141681</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41947</t>
+          <t>42225</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>70919</t>
+          <t>69088</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17449</t>
+          <t>17548</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37149</t>
+          <t>38359</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>64538</t>
+          <t>65114</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>99784</t>
+          <t>100540</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>105489</t>
+          <t>106245</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>138241</t>
+          <t>142344</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>79795</t>
+          <t>77817</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>113058</t>
+          <t>113355</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>195971</t>
+          <t>194477</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>246188</t>
+          <t>243126</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>36,66%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12584</t>
+          <t>12544</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31321</t>
+          <t>31236</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>66620</t>
+          <t>66839</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>98925</t>
+          <t>99622</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>85266</t>
+          <t>86230</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>123216</t>
+          <t>125107</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8179</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22901</t>
+          <t>23437</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>19996</t>
+          <t>20314</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>41134</t>
+          <t>42195</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>31892</t>
+          <t>32069</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>58331</t>
+          <t>58338</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8803</t>
+          <t>8861</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25582</t>
+          <t>24636</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>44651</t>
+          <t>44056</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>72834</t>
+          <t>72766</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>57884</t>
+          <t>57902</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>92173</t>
+          <t>90190</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19159</t>
+          <t>19761</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>40716</t>
+          <t>42260</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16757</t>
+          <t>15917</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36563</t>
+          <t>36245</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40539</t>
+          <t>40677</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>70716</t>
+          <t>69806</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>275743</t>
+          <t>275737</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>309307</t>
+          <t>308353</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>176856</t>
+          <t>175150</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>215754</t>
+          <t>217010</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>460479</t>
+          <t>460292</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>514092</t>
+          <t>513823</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,43%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3255</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>16183</t>
+          <t>15610</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>25141</t>
+          <t>25485</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>47655</t>
+          <t>47448</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>32746</t>
+          <t>33002</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>57783</t>
+          <t>59386</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13743</t>
+          <t>14496</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>31112</t>
+          <t>31011</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>24508</t>
+          <t>24024</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>46346</t>
+          <t>44989</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>43989</t>
+          <t>43543</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>71554</t>
+          <t>71758</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20407</t>
+          <t>20900</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>42029</t>
+          <t>40842</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>37948</t>
+          <t>38414</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>63676</t>
+          <t>63868</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>63718</t>
+          <t>64310</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>96981</t>
+          <t>98888</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,88%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>23315</t>
+          <t>23532</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>45158</t>
+          <t>45721</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>18373</t>
+          <t>18859</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>38771</t>
+          <t>39268</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>48135</t>
+          <t>48334</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>76868</t>
+          <t>77091</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>102181</t>
+          <t>103456</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>133582</t>
+          <t>133351</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>57993</t>
+          <t>58084</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>88253</t>
+          <t>87163</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>172826</t>
+          <t>171344</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>213908</t>
+          <t>211379</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>48,91%</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>28698</t>
+          <t>28395</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>52335</t>
+          <t>52204</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>58412</t>
+          <t>58154</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>88405</t>
+          <t>88566</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>93116</t>
+          <t>93494</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>132565</t>
+          <t>130862</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,62%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>20514</t>
+          <t>20958</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>42263</t>
+          <t>41879</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>25653</t>
+          <t>25131</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>48561</t>
+          <t>47153</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>52421</t>
+          <t>51933</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>83477</t>
+          <t>82923</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,97%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>37464</t>
+          <t>35724</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>63814</t>
+          <t>63238</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>43727</t>
+          <t>43797</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>70466</t>
+          <t>69760</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>87948</t>
+          <t>88594</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>126285</t>
+          <t>125738</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,7%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>45959</t>
+          <t>45943</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>73548</t>
+          <t>73579</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>26101</t>
+          <t>26545</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>48040</t>
+          <t>51059</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,47 +4530,47 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
+          <t>18,23%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>95047</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>77961</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>113160</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
           <t>17,16%</t>
         </is>
       </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>95047</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>77440</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>112807</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>17,16%</t>
-        </is>
-      </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>81987</t>
+          <t>82148</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>113782</t>
+          <t>112948</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>63980</t>
+          <t>62410</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>95081</t>
+          <t>93940</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>151195</t>
+          <t>154433</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>196527</t>
+          <t>199808</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>36,07%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>45322</t>
+          <t>44533</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>75445</t>
+          <t>74160</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>131270</t>
+          <t>130132</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>177568</t>
+          <t>176386</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>184100</t>
+          <t>181705</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>239341</t>
+          <t>238350</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>48842</t>
+          <t>47808</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>82492</t>
+          <t>81691</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>77451</t>
+          <t>75655</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>114332</t>
+          <t>113065</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>137064</t>
+          <t>135692</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>185400</t>
+          <t>186555</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,77%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>103186</t>
+          <t>104345</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>148025</t>
+          <t>147193</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>124341</t>
+          <t>123814</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>166670</t>
+          <t>167476</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>238952</t>
+          <t>239615</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>296701</t>
+          <t>302258</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>116419</t>
+          <t>114407</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>159257</t>
+          <t>158305</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>59944</t>
+          <t>58910</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>93423</t>
+          <t>92165</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>187349</t>
+          <t>183351</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>240654</t>
+          <t>239185</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,66%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>253641</t>
+          <t>253206</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>306282</t>
+          <t>306280</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>201236</t>
+          <t>201121</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>253257</t>
+          <t>253252</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>471150</t>
+          <t>470075</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>547769</t>
+          <t>546388</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,33%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>25969</t>
+          <t>25009</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>51044</t>
+          <t>51323</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>70812</t>
+          <t>71693</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>111025</t>
+          <t>105340</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>100004</t>
+          <t>101653</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>147482</t>
+          <t>146524</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>85089</t>
+          <t>85917</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>123630</t>
+          <t>124397</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>168398</t>
+          <t>167507</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>217028</t>
+          <t>216945</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>268474</t>
+          <t>263514</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>333922</t>
+          <t>326920</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>121817</t>
+          <t>125077</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>169652</t>
+          <t>171436</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>148074</t>
+          <t>147064</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>195257</t>
+          <t>196417</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>285045</t>
+          <t>291731</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>356571</t>
+          <t>356687</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>53956</t>
+          <t>53493</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>85308</t>
+          <t>84842</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>51771</t>
+          <t>50080</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>84798</t>
+          <t>83450</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>111320</t>
+          <t>114683</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>157320</t>
+          <t>160567</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>393075</t>
+          <t>395867</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>449210</t>
+          <t>451003</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>273293</t>
+          <t>275229</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>328995</t>
+          <t>330221</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>681665</t>
+          <t>683314</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>764012</t>
+          <t>761245</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,71%</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>238341</t>
+          <t>237615</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>299975</t>
+          <t>301341</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6202,12 +6202,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>661393</t>
+          <t>660646</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>760420</t>
+          <t>762143</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>916521</t>
+          <t>916001</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>1034154</t>
+          <t>1042034</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -6300,12 +6300,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>284021</t>
+          <t>284772</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>351772</t>
+          <t>354953</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>478189</t>
+          <t>477316</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>562433</t>
+          <t>565190</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>785808</t>
+          <t>772834</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>900498</t>
+          <t>893190</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>470397</t>
+          <t>474972</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>561053</t>
+          <t>560350</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>612613</t>
+          <t>610985</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>704010</t>
+          <t>706379</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>1108717</t>
+          <t>1108671</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>1243764</t>
+          <t>1242232</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6526,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>402097</t>
+          <t>399369</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>481800</t>
+          <t>481606</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>272407</t>
+          <t>271802</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>343370</t>
+          <t>340699</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6596,12 +6596,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>695039</t>
+          <t>697794</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>805493</t>
+          <t>803616</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -6639,12 +6639,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1822258</t>
+          <t>1814879</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>1937460</t>
+          <t>1941264</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>1297622</t>
+          <t>1301373</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1415904</t>
+          <t>1419168</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>3159503</t>
+          <t>3154236</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>3326108</t>
+          <t>3330002</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,78%</t>
         </is>
       </c>
     </row>
@@ -7105,12 +7105,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45341</t>
+          <t>45235</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>73660</t>
+          <t>74769</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>138362</t>
+          <t>138050</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>171905</t>
+          <t>173724</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>191874</t>
+          <t>192465</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>237958</t>
+          <t>240518</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>41,29%</t>
         </is>
       </c>
     </row>
@@ -7218,12 +7218,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9559</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26350</t>
+          <t>25970</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25357</t>
+          <t>26402</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46488</t>
+          <t>48559</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40779</t>
+          <t>40613</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69013</t>
+          <t>68334</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -7331,12 +7331,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18230</t>
+          <t>18725</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39987</t>
+          <t>39563</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15316</t>
+          <t>15003</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34039</t>
+          <t>33259</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38923</t>
+          <t>37882</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>65531</t>
+          <t>64679</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -7444,12 +7444,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13187</t>
+          <t>13353</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31970</t>
+          <t>33368</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>5691</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21837</t>
+          <t>20387</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22759</t>
+          <t>23100</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46807</t>
+          <t>47327</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7529,12 +7529,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>151453</t>
+          <t>151712</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>186680</t>
+          <t>185566</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>49164</t>
+          <t>48860</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>78873</t>
+          <t>78971</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>205827</t>
+          <t>207031</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>255339</t>
+          <t>254890</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,76%</t>
         </is>
       </c>
     </row>
@@ -7787,12 +7787,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45208</t>
+          <t>44150</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74641</t>
+          <t>74805</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>112921</t>
+          <t>112547</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>154398</t>
+          <t>153566</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>168265</t>
+          <t>166284</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>219719</t>
+          <t>216043</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>184450</t>
+          <t>183242</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>229524</t>
+          <t>228835</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>215849</t>
+          <t>214668</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>262150</t>
+          <t>261371</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>412535</t>
+          <t>414968</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>475088</t>
+          <t>479522</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,85%</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>83411</t>
+          <t>85504</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>121769</t>
+          <t>123201</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>61412</t>
+          <t>62495</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>95245</t>
+          <t>95873</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>155325</t>
+          <t>154163</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>203694</t>
+          <t>205115</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,04%</t>
         </is>
       </c>
     </row>
@@ -8126,12 +8126,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13470</t>
+          <t>12780</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31138</t>
+          <t>30030</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6876</t>
+          <t>6570</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21231</t>
+          <t>21098</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22887</t>
+          <t>22597</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45862</t>
+          <t>46971</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -8239,12 +8239,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>95692</t>
+          <t>95781</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>133568</t>
+          <t>133783</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47970</t>
+          <t>45796</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>79182</t>
+          <t>77873</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>150811</t>
+          <t>151138</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>200878</t>
+          <t>201398</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11739</t>
+          <t>12317</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27859</t>
+          <t>28650</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35561</t>
+          <t>35180</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62775</t>
+          <t>62076</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53285</t>
+          <t>51841</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84431</t>
+          <t>82325</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13815</t>
+          <t>14092</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31580</t>
+          <t>33161</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17147</t>
+          <t>17045</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36410</t>
+          <t>36567</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35442</t>
+          <t>35569</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61201</t>
+          <t>61876</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22569</t>
+          <t>23031</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>42649</t>
+          <t>43374</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>94767</t>
+          <t>95205</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>128945</t>
+          <t>129711</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>123003</t>
+          <t>123377</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>164269</t>
+          <t>166748</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,53%</t>
         </is>
       </c>
     </row>
@@ -8808,12 +8808,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>66273</t>
+          <t>64413</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>96632</t>
+          <t>97342</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55795</t>
+          <t>55048</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>84553</t>
+          <t>85235</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>128097</t>
+          <t>128336</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>169341</t>
+          <t>169266</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -8921,12 +8921,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>148030</t>
+          <t>146037</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>180897</t>
+          <t>181571</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8956,12 +8956,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>67336</t>
+          <t>67529</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>98612</t>
+          <t>98860</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8991,12 +8991,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>224402</t>
+          <t>224706</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>272157</t>
+          <t>271266</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,54%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52237</t>
+          <t>51108</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>82445</t>
+          <t>81192</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>105450</t>
+          <t>104721</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>141829</t>
+          <t>141759</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>166038</t>
+          <t>164361</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>214270</t>
+          <t>214341</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,34%</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>27482</t>
+          <t>26664</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>52618</t>
+          <t>52195</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>33610</t>
+          <t>34995</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>60338</t>
+          <t>62051</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>67276</t>
+          <t>68511</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>103421</t>
+          <t>104078</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9377,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22536</t>
+          <t>22100</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>44948</t>
+          <t>43827</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>28748</t>
+          <t>28119</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>53168</t>
+          <t>52152</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>56683</t>
+          <t>56620</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>87440</t>
+          <t>88972</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,76%</t>
         </is>
       </c>
     </row>
@@ -9490,12 +9490,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18094</t>
+          <t>18709</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>40340</t>
+          <t>39537</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13127</t>
+          <t>13615</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31996</t>
+          <t>31481</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>37351</t>
+          <t>36460</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>64707</t>
+          <t>64405</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -9603,12 +9603,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>183888</t>
+          <t>185673</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>223844</t>
+          <t>224446</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>137971</t>
+          <t>137802</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>177942</t>
+          <t>177768</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>333791</t>
+          <t>331792</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>390906</t>
+          <t>388911</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,42%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11080</t>
+          <t>10156</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8640</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>23272</t>
+          <t>23496</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>12039</t>
+          <t>11559</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>28196</t>
+          <t>28946</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -9946,12 +9946,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>26412</t>
+          <t>26273</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>47818</t>
+          <t>47496</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9981,12 +9981,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>42545</t>
+          <t>42414</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>67027</t>
+          <t>66240</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>75720</t>
+          <t>73372</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>107211</t>
+          <t>106257</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,72%</t>
         </is>
       </c>
     </row>
@@ -10059,12 +10059,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18885</t>
+          <t>19099</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>37573</t>
+          <t>39839</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>31729</t>
+          <t>32553</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>56237</t>
+          <t>55996</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>57278</t>
+          <t>56512</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>85403</t>
+          <t>86257</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -10172,12 +10172,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>22200</t>
+          <t>22298</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>45507</t>
+          <t>44252</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>21274</t>
+          <t>21631</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>41453</t>
+          <t>41631</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>50042</t>
+          <t>48545</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>78878</t>
+          <t>79119</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,41%</t>
         </is>
       </c>
     </row>
@@ -10285,12 +10285,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>96139</t>
+          <t>95139</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>125228</t>
+          <t>125419</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10300,12 +10300,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>63166</t>
+          <t>62023</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>91325</t>
+          <t>90426</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>166624</t>
+          <t>166660</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>206523</t>
+          <t>208928</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>48,61%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>23423</t>
+          <t>23546</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>46333</t>
+          <t>46671</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>32252</t>
+          <t>32509</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>55291</t>
+          <t>55979</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>62543</t>
+          <t>62518</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>94489</t>
+          <t>96209</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -10628,12 +10628,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>34567</t>
+          <t>34280</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>58318</t>
+          <t>59096</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10643,12 +10643,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10663,12 +10663,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>44909</t>
+          <t>44750</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>72360</t>
+          <t>70703</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>84047</t>
+          <t>84085</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>121255</t>
+          <t>121661</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10718,7 +10718,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,03%</t>
         </is>
       </c>
     </row>
@@ -10741,12 +10741,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>18309</t>
+          <t>18164</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>38439</t>
+          <t>37178</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10756,12 +10756,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10776,12 +10776,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>24379</t>
+          <t>25105</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>46382</t>
+          <t>46140</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10811,12 +10811,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>48676</t>
+          <t>48034</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>77568</t>
+          <t>78687</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10826,12 +10826,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -10854,12 +10854,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5136</t>
+          <t>5028</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>19133</t>
+          <t>19484</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2831</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>12881</t>
+          <t>13427</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10904,12 +10904,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>9498</t>
+          <t>10449</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>26851</t>
+          <t>27029</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10939,12 +10939,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -10967,12 +10967,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>127716</t>
+          <t>125395</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>160600</t>
+          <t>158680</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10982,12 +10982,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>110270</t>
+          <t>111555</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>142594</t>
+          <t>143642</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11017,12 +11017,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>247429</t>
+          <t>245591</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>292940</t>
+          <t>293871</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11052,12 +11052,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>55,62%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>36404</t>
+          <t>36369</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>64208</t>
+          <t>66236</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>104224</t>
+          <t>104465</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>146336</t>
+          <t>147353</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>148420</t>
+          <t>149520</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>198199</t>
+          <t>198384</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -11310,12 +11310,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>68105</t>
+          <t>66978</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>102983</t>
+          <t>102676</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11325,12 +11325,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11345,12 +11345,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>99526</t>
+          <t>97322</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>139917</t>
+          <t>139522</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11360,12 +11360,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>176790</t>
+          <t>174137</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>231325</t>
+          <t>229784</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,22%</t>
         </is>
       </c>
     </row>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>82611</t>
+          <t>83849</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>123715</t>
+          <t>123941</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>107890</t>
+          <t>107824</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>149161</t>
+          <t>149424</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>201216</t>
+          <t>199303</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>258651</t>
+          <t>255303</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11508,12 +11508,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -11536,12 +11536,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>93277</t>
+          <t>94074</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>133699</t>
+          <t>134581</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>63132</t>
+          <t>64891</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>97291</t>
+          <t>100173</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>166570</t>
+          <t>166764</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>219058</t>
+          <t>221311</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11621,12 +11621,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -11649,12 +11649,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>274282</t>
+          <t>274562</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>327290</t>
+          <t>327367</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>212085</t>
+          <t>211561</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>263089</t>
+          <t>263878</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11699,12 +11699,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>506137</t>
+          <t>501721</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>582663</t>
+          <t>575074</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11734,12 +11734,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,1%</t>
         </is>
       </c>
     </row>
@@ -11879,12 +11879,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>32462</t>
+          <t>32713</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>60325</t>
+          <t>59191</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>78720</t>
+          <t>82382</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>119002</t>
+          <t>121278</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11949,12 +11949,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>119272</t>
+          <t>121406</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>165849</t>
+          <t>166704</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11964,12 +11964,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>173392</t>
+          <t>174379</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>223248</t>
+          <t>224628</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12007,12 +12007,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12027,12 +12027,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>313936</t>
+          <t>314058</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>376543</t>
+          <t>372213</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12042,12 +12042,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12062,12 +12062,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>501918</t>
+          <t>505473</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>580863</t>
+          <t>580965</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,3%</t>
         </is>
       </c>
     </row>
@@ -12105,12 +12105,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>163141</t>
+          <t>161319</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>210221</t>
+          <t>208974</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12120,12 +12120,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12140,12 +12140,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>148165</t>
+          <t>147422</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>195795</t>
+          <t>197332</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12155,12 +12155,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>321278</t>
+          <t>324128</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>390707</t>
+          <t>385432</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12190,12 +12190,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,08%</t>
         </is>
       </c>
     </row>
@@ -12218,12 +12218,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>77961</t>
+          <t>75408</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>111357</t>
+          <t>114515</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>41403</t>
+          <t>41553</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>71085</t>
+          <t>70652</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12268,12 +12268,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>126097</t>
+          <t>124868</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>172994</t>
+          <t>171454</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12303,12 +12303,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -12331,12 +12331,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>225741</t>
+          <t>227701</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>279476</t>
+          <t>281846</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>136251</t>
+          <t>133643</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>185770</t>
+          <t>182199</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12381,12 +12381,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>375751</t>
+          <t>375169</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>447662</t>
+          <t>444948</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12416,12 +12416,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,8%</t>
         </is>
       </c>
     </row>
@@ -12561,12 +12561,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>301654</t>
+          <t>302487</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>371322</t>
+          <t>372784</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12576,12 +12576,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12596,12 +12596,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>689529</t>
+          <t>692019</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>784511</t>
+          <t>792978</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12611,12 +12611,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12631,12 +12631,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>1005046</t>
+          <t>1008203</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>1134760</t>
+          <t>1134726</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12646,7 +12646,7 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -12674,12 +12674,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>602023</t>
+          <t>603562</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>692471</t>
+          <t>694636</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>868070</t>
+          <t>867576</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>977602</t>
+          <t>976943</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12724,12 +12724,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1500954</t>
+          <t>1496288</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>1639322</t>
+          <t>1647704</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,85%</t>
         </is>
       </c>
     </row>
@@ -12787,12 +12787,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>492040</t>
+          <t>487993</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>579463</t>
+          <t>576780</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>578316</t>
+          <t>580591</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>668315</t>
+          <t>670217</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12837,12 +12837,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>1101547</t>
+          <t>1095896</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>1222539</t>
+          <t>1223810</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12872,12 +12872,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -12900,12 +12900,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>364918</t>
+          <t>361922</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>441971</t>
+          <t>438995</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>254995</t>
+          <t>253669</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>323173</t>
+          <t>321140</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12950,12 +12950,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>637369</t>
+          <t>640149</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>737097</t>
+          <t>739219</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12985,12 +12985,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -13013,12 +13013,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1399609</t>
+          <t>1404912</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>1511904</t>
+          <t>1517238</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13028,12 +13028,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13048,12 +13048,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>908927</t>
+          <t>909067</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1016924</t>
+          <t>1019554</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13063,12 +13063,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13083,12 +13083,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>2344262</t>
+          <t>2338813</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>2502378</t>
+          <t>2499960</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13098,12 +13098,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,19%</t>
         </is>
       </c>
     </row>
